--- a/VerveStacks_KEN_grids_kan10/vt_vervestacks_KEN_v1.xlsx
+++ b/VerveStacks_KEN_grids_kan10/vt_vervestacks_KEN_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_KEN_grids_kan10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B324DE28-A2FE-4BED-8D3A-623FB1A8B855}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D8F322D7-01C0-465B-B064-AA7363B3F4D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{5CEDBE63-7600-4717-8536-6E6558195BB6}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{5BC8FD11-4F9D-48A6-A9F1-4831C9035F3F}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -1246,7 +1246,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5C7BB6D-2AE5-41A9-BF4E-F2D4D0EDAF43}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35165D1A-AA76-4B4C-827E-0C4D06DE8C60}">
   <dimension ref="B9:V18"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1822,7 +1822,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB740ACE-F64F-4880-B7F1-65AE1A2FF7B2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6AAE783-0F82-4502-A5CF-2103BB1C611E}">
   <dimension ref="B9:W54"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -4519,7 +4519,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D1AC53D-2928-4A57-BFEA-1BF182B79454}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBC10B37-276E-438E-80CE-469CCF03FD71}">
   <dimension ref="B9:W85"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -8814,7 +8814,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71B6C9E2-D85C-4253-B29C-A71A9CDF3F3F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20047266-F595-41C7-82B1-A676D8D26BCA}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>
